--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$2</c:f>
+              <c:f>Data!$A$2:$A$3</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$2</c:f>
+              <c:f>Data!$C$2:$C$3</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -398,8 +398,38 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-28 23:47:45</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>200182</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -456,13 +486,13 @@
         <v>186993</v>
       </c>
       <c r="C2">
-        <v>186993</v>
+        <v>200182</v>
       </c>
       <c r="D2">
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>186993</v>
+        <v>200182</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$3</c:f>
+              <c:f>Data!$A$2:$A$4</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$3</c:f>
+              <c:f>Data!$C$2:$C$4</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -428,8 +428,38 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:38:49</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>199111</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -492,7 +522,7 @@
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>200182</v>
+        <v>199111</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$4</c:f>
+              <c:f>Data!$A$2:$A$5</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$4</c:f>
+              <c:f>Data!$C$2:$C$5</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -458,8 +458,40 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:08:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WinHttpSendRequest failed.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$5</c:f>
+              <c:f>Data!$A$2:$A$4</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$5</c:f>
+              <c:f>Data!$C$2:$C$4</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -458,40 +458,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-29 14:08:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>WinHttpSendRequest failed.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$4</c:f>
+              <c:f>Data!$A$2:$A$5</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$4</c:f>
+              <c:f>Data!$C$2:$C$5</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -458,8 +458,38 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:01:31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>197667</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -522,7 +552,7 @@
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>199111</v>
+        <v>197667</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$5</c:f>
+              <c:f>Data!$A$2:$A$6</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$5</c:f>
+              <c:f>Data!$C$2:$C$6</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -488,8 +488,38 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:22:26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>199915</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -552,7 +582,7 @@
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>197667</v>
+        <v>199915</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$6</c:f>
+              <c:f>Data!$A$2:$A$7</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$6</c:f>
+              <c:f>Data!$C$2:$C$7</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -518,8 +518,38 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:28:08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>199967</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -582,7 +612,7 @@
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>199915</v>
+        <v>199967</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$7</c:f>
+              <c:f>Data!$A$2:$A$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$7</c:f>
+              <c:f>Data!$C$2:$C$8</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -548,8 +548,38 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:30:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>199967</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$8</c:f>
+              <c:f>Data!$A$2:$A$9</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$8</c:f>
+              <c:f>Data!$C$2:$C$9</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -578,8 +578,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:33:51</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>199984</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -642,7 +672,7 @@
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>199967</v>
+        <v>199984</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$9</c:f>
+              <c:f>Data!$A$2:$A$5</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$9</c:f>
+              <c:f>Data!$C$2:$C$5</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -488,128 +488,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-30 12:22:26</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>199915</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>parsed joblist hdnGICnt</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-30 12:28:08</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>199967</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>parsed joblist hdnGICnt</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-30 12:30:10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>199967</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>parsed joblist hdnGICnt</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-04-30 12:33:51</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>199984</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>parsed joblist hdnGICnt</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -672,7 +552,7 @@
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>199984</v>
+        <v>197667</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$5</c:f>
+              <c:f>Data!$A$2:$A$6</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$5</c:f>
+              <c:f>Data!$C$2:$C$6</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -488,8 +488,40 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-01 09:01:50</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HTTP failed after 3 attempts: WinHttpSendRequest failed.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -491,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-01 09:01:50</t>
+          <t>2026-05-01 11:53:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -499,19 +499,17 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C6">
+        <v>191130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HTTP failed after 3 attempts: WinHttpSendRequest failed.</t>
+          <t>parsed joblist hdnGICnt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -584,7 +582,7 @@
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>197667</v>
+        <v>191130</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$6</c:f>
+              <c:f>Data!$A$2:$A$7</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$6</c:f>
+              <c:f>Data!$C$2:$C$7</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -518,8 +518,38 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-02 09:01:14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>188018</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -582,7 +612,7 @@
         <v>186993</v>
       </c>
       <c r="E2">
-        <v>191130</v>
+        <v>188018</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$7</c:f>
+              <c:f>Data!$A$2:$A$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$7</c:f>
+              <c:f>Data!$C$2:$C$8</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -548,8 +548,38 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-03 09:01:27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>183487</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -609,10 +639,10 @@
         <v>200182</v>
       </c>
       <c r="D2">
-        <v>186993</v>
+        <v>183487</v>
       </c>
       <c r="E2">
-        <v>188018</v>
+        <v>183487</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$8</c:f>
+              <c:f>Data!$A$2:$A$9</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$8</c:f>
+              <c:f>Data!$C$2:$C$9</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$2</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$3</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$2</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$3</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$2</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$3</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$2</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$3</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$2</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$3</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$2</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$3</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$2</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$3</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$2</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$3</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -578,8 +578,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-04 09:01:34</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>178925</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -645,8 +675,27 @@
         <v>183487</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>178925</v>
+      </c>
+      <c r="C3">
+        <v>178925</v>
+      </c>
+      <c r="D3">
+        <v>178925</v>
+      </c>
+      <c r="E3">
+        <v>178925</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$9</c:f>
+              <c:f>Data!$A$2:$A$10</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$9</c:f>
+              <c:f>Data!$C$2:$C$10</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -608,8 +608,38 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:01:49</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>182502</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -685,13 +715,13 @@
         <v>178925</v>
       </c>
       <c r="C3">
-        <v>178925</v>
+        <v>182502</v>
       </c>
       <c r="D3">
         <v>178925</v>
       </c>
       <c r="E3">
-        <v>178925</v>
+        <v>182502</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$10</c:f>
+              <c:f>Data!$A$2:$A$11</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$10</c:f>
+              <c:f>Data!$C$2:$C$11</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -638,8 +638,38 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:01:47</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>179358</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -721,7 +751,7 @@
         <v>178925</v>
       </c>
       <c r="E3">
-        <v>182502</v>
+        <v>179358</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$11</c:f>
+              <c:f>Data!$A$2:$A$12</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$11</c:f>
+              <c:f>Data!$C$2:$C$12</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -668,8 +668,38 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-07 09:01:22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>183397</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -745,13 +775,13 @@
         <v>178925</v>
       </c>
       <c r="C3">
-        <v>182502</v>
+        <v>183397</v>
       </c>
       <c r="D3">
         <v>178925</v>
       </c>
       <c r="E3">
-        <v>179358</v>
+        <v>183397</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$12</c:f>
+              <c:f>Data!$A$2:$A$13</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$12</c:f>
+              <c:f>Data!$C$2:$C$13</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -698,8 +698,38 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-08 09:01:13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>187523</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -775,13 +805,13 @@
         <v>178925</v>
       </c>
       <c r="C3">
-        <v>183397</v>
+        <v>187523</v>
       </c>
       <c r="D3">
         <v>178925</v>
       </c>
       <c r="E3">
-        <v>183397</v>
+        <v>187523</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$13</c:f>
+              <c:f>Data!$A$2:$A$14</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$13</c:f>
+              <c:f>Data!$C$2:$C$14</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -728,8 +728,38 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:00:58</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>187802</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -805,13 +835,13 @@
         <v>178925</v>
       </c>
       <c r="C3">
-        <v>187523</v>
+        <v>187802</v>
       </c>
       <c r="D3">
         <v>178925</v>
       </c>
       <c r="E3">
-        <v>187523</v>
+        <v>187802</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$14</c:f>
+              <c:f>Data!$A$2:$A$15</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$14</c:f>
+              <c:f>Data!$C$2:$C$15</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -758,8 +758,38 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-10 09:01:30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>183172</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -841,7 +871,7 @@
         <v>178925</v>
       </c>
       <c r="E3">
-        <v>187802</v>
+        <v>183172</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$15</c:f>
+              <c:f>Data!$A$2:$A$16</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$15</c:f>
+              <c:f>Data!$C$2:$C$16</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$3</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$4</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$3</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$4</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$3</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$4</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$3</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$4</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$3</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$4</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$3</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$4</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$3</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$4</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$3</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$4</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -788,8 +788,38 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-11 09:01:42</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>177898</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -874,8 +904,27 @@
         <v>183172</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>177898</v>
+      </c>
+      <c r="C4">
+        <v>177898</v>
+      </c>
+      <c r="D4">
+        <v>177898</v>
+      </c>
+      <c r="E4">
+        <v>177898</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$16</c:f>
+              <c:f>Data!$A$2:$A$17</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$16</c:f>
+              <c:f>Data!$C$2:$C$17</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -818,8 +818,38 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-12 09:01:03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>183567</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -914,13 +944,13 @@
         <v>177898</v>
       </c>
       <c r="C4">
-        <v>177898</v>
+        <v>183567</v>
       </c>
       <c r="D4">
         <v>177898</v>
       </c>
       <c r="E4">
-        <v>177898</v>
+        <v>183567</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$17</c:f>
+              <c:f>Data!$A$2:$A$18</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$17</c:f>
+              <c:f>Data!$C$2:$C$18</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -848,8 +848,38 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:01:22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>187795</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F17"/>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -944,13 +974,13 @@
         <v>177898</v>
       </c>
       <c r="C4">
-        <v>183567</v>
+        <v>187795</v>
       </c>
       <c r="D4">
         <v>177898</v>
       </c>
       <c r="E4">
-        <v>183567</v>
+        <v>187795</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$18</c:f>
+              <c:f>Data!$A$2:$A$19</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$18</c:f>
+              <c:f>Data!$C$2:$C$19</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -878,8 +878,38 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-14 09:01:49</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>190273</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F18"/>
+  <autoFilter ref="A1:F19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -974,13 +1004,13 @@
         <v>177898</v>
       </c>
       <c r="C4">
-        <v>187795</v>
+        <v>190273</v>
       </c>
       <c r="D4">
         <v>177898</v>
       </c>
       <c r="E4">
-        <v>187795</v>
+        <v>190273</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$19</c:f>
+              <c:f>Data!$A$2:$A$20</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$19</c:f>
+              <c:f>Data!$C$2:$C$20</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -908,8 +908,38 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-15 09:00:56</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>192911</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F19"/>
+  <autoFilter ref="A1:F20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1004,13 +1034,13 @@
         <v>177898</v>
       </c>
       <c r="C4">
-        <v>190273</v>
+        <v>192911</v>
       </c>
       <c r="D4">
         <v>177898</v>
       </c>
       <c r="E4">
-        <v>190273</v>
+        <v>192911</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$20</c:f>
+              <c:f>Data!$A$2:$A$21</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$20</c:f>
+              <c:f>Data!$C$2:$C$21</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -938,8 +938,38 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-16 09:01:25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>192353</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F20"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1040,7 +1070,7 @@
         <v>177898</v>
       </c>
       <c r="E4">
-        <v>192911</v>
+        <v>192353</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$21</c:f>
+              <c:f>Data!$A$2:$A$22</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$21</c:f>
+              <c:f>Data!$C$2:$C$22</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -968,8 +968,38 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-17 09:01:21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>187921</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F21"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1070,7 +1100,7 @@
         <v>177898</v>
       </c>
       <c r="E4">
-        <v>192353</v>
+        <v>187921</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$22</c:f>
+              <c:f>Data!$A$2:$A$23</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$22</c:f>
+              <c:f>Data!$C$2:$C$23</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$4</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$5</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$4</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$5</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$4</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$5</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$4</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$5</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$4</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$5</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$4</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$5</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$4</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$5</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$4</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$5</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -998,8 +998,38 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-18 09:01:47</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>183323</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A1:F23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1103,8 +1133,27 @@
         <v>187921</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>183323</v>
+      </c>
+      <c r="C5">
+        <v>183323</v>
+      </c>
+      <c r="D5">
+        <v>183323</v>
+      </c>
+      <c r="E5">
+        <v>183323</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$23</c:f>
+              <c:f>Data!$A$2:$A$24</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$23</c:f>
+              <c:f>Data!$C$2:$C$24</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1028,8 +1028,38 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-19 09:01:23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>188495</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F23"/>
+  <autoFilter ref="A1:F24"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1143,13 +1173,13 @@
         <v>183323</v>
       </c>
       <c r="C5">
-        <v>183323</v>
+        <v>188495</v>
       </c>
       <c r="D5">
         <v>183323</v>
       </c>
       <c r="E5">
-        <v>183323</v>
+        <v>188495</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$24</c:f>
+              <c:f>Data!$A$2:$A$25</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$24</c:f>
+              <c:f>Data!$C$2:$C$25</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1058,8 +1058,38 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:01:24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>192955</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F24"/>
+  <autoFilter ref="A1:F25"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1173,13 +1203,13 @@
         <v>183323</v>
       </c>
       <c r="C5">
-        <v>188495</v>
+        <v>192955</v>
       </c>
       <c r="D5">
         <v>183323</v>
       </c>
       <c r="E5">
-        <v>188495</v>
+        <v>192955</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$25</c:f>
+              <c:f>Data!$A$2:$A$26</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$25</c:f>
+              <c:f>Data!$C$2:$C$26</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1088,8 +1088,38 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:01:01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>194781</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F25"/>
+  <autoFilter ref="A1:F26"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1203,13 +1233,13 @@
         <v>183323</v>
       </c>
       <c r="C5">
-        <v>192955</v>
+        <v>194781</v>
       </c>
       <c r="D5">
         <v>183323</v>
       </c>
       <c r="E5">
-        <v>192955</v>
+        <v>194781</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$26</c:f>
+              <c:f>Data!$A$2:$A$27</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$26</c:f>
+              <c:f>Data!$C$2:$C$27</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1118,8 +1118,38 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:01:12</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>197011</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F26"/>
+  <autoFilter ref="A1:F27"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1233,13 +1263,13 @@
         <v>183323</v>
       </c>
       <c r="C5">
-        <v>194781</v>
+        <v>197011</v>
       </c>
       <c r="D5">
         <v>183323</v>
       </c>
       <c r="E5">
-        <v>194781</v>
+        <v>197011</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$27</c:f>
+              <c:f>Data!$A$2:$A$28</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$27</c:f>
+              <c:f>Data!$C$2:$C$28</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1148,8 +1148,40 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-23 09:00:36</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HTTP failed after 3 attempts: WinHttpSendRequest failed.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F27"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -1151,7 +1151,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 09:00:36</t>
+          <t>2026-05-23 09:11:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1159,19 +1159,17 @@
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C28">
+        <v>196434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HTTP failed after 3 attempts: WinHttpSendRequest failed.</t>
+          <t>parsed joblist hdnGICnt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1301,7 +1299,7 @@
         <v>183323</v>
       </c>
       <c r="E5">
-        <v>197011</v>
+        <v>196434</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$28</c:f>
+              <c:f>Data!$A$2:$A$29</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$28</c:f>
+              <c:f>Data!$C$2:$C$29</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1178,8 +1178,38 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-24 09:00:50</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>192086</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F28"/>
+  <autoFilter ref="A1:F29"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1299,7 +1329,7 @@
         <v>183323</v>
       </c>
       <c r="E5">
-        <v>196434</v>
+        <v>192086</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$29</c:f>
+              <c:f>Data!$A$2:$A$30</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$29</c:f>
+              <c:f>Data!$C$2:$C$30</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$5</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$6</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$5</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$6</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$5</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$6</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$5</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$6</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$5</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$6</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$5</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$6</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$5</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$6</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$5</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$6</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1208,8 +1208,38 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:01:41</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>187811</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1332,8 +1362,27 @@
         <v>192086</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>187811</v>
+      </c>
+      <c r="C6">
+        <v>187811</v>
+      </c>
+      <c r="D6">
+        <v>187811</v>
+      </c>
+      <c r="E6">
+        <v>187811</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$30</c:f>
+              <c:f>Data!$A$2:$A$31</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$30</c:f>
+              <c:f>Data!$C$2:$C$31</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1238,8 +1238,38 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:01:20</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>184088</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F30"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1375,10 +1405,10 @@
         <v>187811</v>
       </c>
       <c r="D6">
-        <v>187811</v>
+        <v>184088</v>
       </c>
       <c r="E6">
-        <v>187811</v>
+        <v>184088</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$31</c:f>
+              <c:f>Data!$A$2:$A$32</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$31</c:f>
+              <c:f>Data!$C$2:$C$32</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1268,8 +1268,38 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:01:26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>189613</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F31"/>
+  <autoFilter ref="A1:F32"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1402,13 +1432,13 @@
         <v>187811</v>
       </c>
       <c r="C6">
-        <v>187811</v>
+        <v>189613</v>
       </c>
       <c r="D6">
         <v>184088</v>
       </c>
       <c r="E6">
-        <v>184088</v>
+        <v>189613</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$32</c:f>
+              <c:f>Data!$A$2:$A$33</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$32</c:f>
+              <c:f>Data!$C$2:$C$33</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1298,8 +1298,38 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-28 09:01:12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>192886</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F32"/>
+  <autoFilter ref="A1:F33"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1432,13 +1462,13 @@
         <v>187811</v>
       </c>
       <c r="C6">
-        <v>189613</v>
+        <v>192886</v>
       </c>
       <c r="D6">
         <v>184088</v>
       </c>
       <c r="E6">
-        <v>189613</v>
+        <v>192886</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$33</c:f>
+              <c:f>Data!$A$2:$A$34</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$33</c:f>
+              <c:f>Data!$C$2:$C$34</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1328,8 +1328,38 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:00:44</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>195225</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F33"/>
+  <autoFilter ref="A1:F34"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1462,13 +1492,13 @@
         <v>187811</v>
       </c>
       <c r="C6">
-        <v>192886</v>
+        <v>195225</v>
       </c>
       <c r="D6">
         <v>184088</v>
       </c>
       <c r="E6">
-        <v>192886</v>
+        <v>195225</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$34</c:f>
+              <c:f>Data!$A$2:$A$35</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$34</c:f>
+              <c:f>Data!$C$2:$C$35</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1358,8 +1358,38 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30 09:01:44</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>195037</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F34"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1498,7 +1528,7 @@
         <v>184088</v>
       </c>
       <c r="E6">
-        <v>195225</v>
+        <v>195037</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$35</c:f>
+              <c:f>Data!$A$2:$A$36</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$35</c:f>
+              <c:f>Data!$C$2:$C$36</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1388,8 +1388,38 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-31 09:01:13</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>190116</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F35"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1528,7 +1558,7 @@
         <v>184088</v>
       </c>
       <c r="E6">
-        <v>195037</v>
+        <v>190116</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$36</c:f>
+              <c:f>Data!$A$2:$A$37</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$36</c:f>
+              <c:f>Data!$C$2:$C$37</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$6</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$7</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$6</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$7</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$6</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$7</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$6</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$7</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$6</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$7</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$6</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$7</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$6</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$7</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$6</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$7</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1418,8 +1418,38 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-01 09:01:22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>180449</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F36"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1561,8 +1591,27 @@
         <v>190116</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>180449</v>
+      </c>
+      <c r="C7">
+        <v>180449</v>
+      </c>
+      <c r="D7">
+        <v>180449</v>
+      </c>
+      <c r="E7">
+        <v>180449</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$37</c:f>
+              <c:f>Data!$A$2:$A$38</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$37</c:f>
+              <c:f>Data!$C$2:$C$38</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1448,8 +1448,38 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-02 09:00:51</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>186549</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1601,13 +1631,13 @@
         <v>180449</v>
       </c>
       <c r="C7">
-        <v>180449</v>
+        <v>186549</v>
       </c>
       <c r="D7">
         <v>180449</v>
       </c>
       <c r="E7">
-        <v>180449</v>
+        <v>186549</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$38</c:f>
+              <c:f>Data!$A$2:$A$39</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$38</c:f>
+              <c:f>Data!$C$2:$C$39</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1478,8 +1478,38 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:01:16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>190777</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F38"/>
+  <autoFilter ref="A1:F39"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1631,13 +1661,13 @@
         <v>180449</v>
       </c>
       <c r="C7">
-        <v>186549</v>
+        <v>190777</v>
       </c>
       <c r="D7">
         <v>180449</v>
       </c>
       <c r="E7">
-        <v>186549</v>
+        <v>190777</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$39</c:f>
+              <c:f>Data!$A$2:$A$40</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$39</c:f>
+              <c:f>Data!$C$2:$C$40</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1508,8 +1508,38 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:01:11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>187906</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1667,7 +1697,7 @@
         <v>180449</v>
       </c>
       <c r="E7">
-        <v>190777</v>
+        <v>187906</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$40</c:f>
+              <c:f>Data!$A$2:$A$41</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$40</c:f>
+              <c:f>Data!$C$2:$C$41</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1538,8 +1538,40 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-05 09:00:55</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HTTP failed after 3 attempts: WinHttpSendRequest failed.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F40"/>
+  <autoFilter ref="A1:F41"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -1541,7 +1541,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-05 09:00:55</t>
+          <t>2026-06-05 09:46:39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1549,19 +1549,17 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C41">
+        <v>194086</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HTTP failed after 3 attempts: WinHttpSendRequest failed.</t>
+          <t>parsed joblist hdnGICnt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1723,13 +1721,13 @@
         <v>180449</v>
       </c>
       <c r="C7">
-        <v>190777</v>
+        <v>194086</v>
       </c>
       <c r="D7">
         <v>180449</v>
       </c>
       <c r="E7">
-        <v>187906</v>
+        <v>194086</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$41</c:f>
+              <c:f>Data!$A$2:$A$42</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$41</c:f>
+              <c:f>Data!$C$2:$C$42</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1568,8 +1568,38 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:00:36</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>193724</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F41"/>
+  <autoFilter ref="A1:F42"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1727,7 +1757,7 @@
         <v>180449</v>
       </c>
       <c r="E7">
-        <v>194086</v>
+        <v>193724</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$42</c:f>
+              <c:f>Data!$A$2:$A$43</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$42</c:f>
+              <c:f>Data!$C$2:$C$43</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1598,8 +1598,38 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-07 09:00:36</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>189098</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F42"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1757,7 +1787,7 @@
         <v>180449</v>
       </c>
       <c r="E7">
-        <v>193724</v>
+        <v>189098</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$43</c:f>
+              <c:f>Data!$A$2:$A$44</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$43</c:f>
+              <c:f>Data!$C$2:$C$44</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$7</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$7</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$8</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$7</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$7</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$8</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$7</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$7</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$8</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$7</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$7</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$8</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1628,8 +1628,38 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-08 09:00:36</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>184074</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F44"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1790,8 +1820,27 @@
         <v>189098</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>184074</v>
+      </c>
+      <c r="C8">
+        <v>184074</v>
+      </c>
+      <c r="D8">
+        <v>184074</v>
+      </c>
+      <c r="E8">
+        <v>184074</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E7"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$44</c:f>
+              <c:f>Data!$A$2:$A$45</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$44</c:f>
+              <c:f>Data!$C$2:$C$45</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1658,8 +1658,38 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-09 09:00:36</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>190135</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F44"/>
+  <autoFilter ref="A1:F45"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1830,13 +1860,13 @@
         <v>184074</v>
       </c>
       <c r="C8">
-        <v>184074</v>
+        <v>190135</v>
       </c>
       <c r="D8">
         <v>184074</v>
       </c>
       <c r="E8">
-        <v>184074</v>
+        <v>190135</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$45</c:f>
+              <c:f>Data!$A$2:$A$46</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$45</c:f>
+              <c:f>Data!$C$2:$C$46</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1688,8 +1688,38 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-10 09:00:36</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>194450</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F45"/>
+  <autoFilter ref="A1:F46"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1860,13 +1890,13 @@
         <v>184074</v>
       </c>
       <c r="C8">
-        <v>190135</v>
+        <v>194450</v>
       </c>
       <c r="D8">
         <v>184074</v>
       </c>
       <c r="E8">
-        <v>190135</v>
+        <v>194450</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$46</c:f>
+              <c:f>Data!$A$2:$A$47</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$46</c:f>
+              <c:f>Data!$C$2:$C$47</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1718,8 +1718,38 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:00:36</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>195968</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F46"/>
+  <autoFilter ref="A1:F47"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1890,13 +1920,13 @@
         <v>184074</v>
       </c>
       <c r="C8">
-        <v>194450</v>
+        <v>195968</v>
       </c>
       <c r="D8">
         <v>184074</v>
       </c>
       <c r="E8">
-        <v>194450</v>
+        <v>195968</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$47</c:f>
+              <c:f>Data!$A$2:$A$48</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$47</c:f>
+              <c:f>Data!$C$2:$C$48</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1748,8 +1748,38 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:00:36</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>198461</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:F48"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1920,13 +1950,13 @@
         <v>184074</v>
       </c>
       <c r="C8">
-        <v>195968</v>
+        <v>198461</v>
       </c>
       <c r="D8">
         <v>184074</v>
       </c>
       <c r="E8">
-        <v>195968</v>
+        <v>198461</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$48</c:f>
+              <c:f>Data!$A$2:$A$49</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$48</c:f>
+              <c:f>Data!$C$2:$C$49</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1778,8 +1778,38 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-13 09:00:36</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>197870</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F48"/>
+  <autoFilter ref="A1:F49"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1956,7 +1986,7 @@
         <v>184074</v>
       </c>
       <c r="E8">
-        <v>198461</v>
+        <v>197870</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$49</c:f>
+              <c:f>Data!$A$2:$A$50</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$49</c:f>
+              <c:f>Data!$C$2:$C$50</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1808,8 +1808,38 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-14 09:00:36</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>193353</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F49"/>
+  <autoFilter ref="A1:F50"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1986,7 +2016,7 @@
         <v>184074</v>
       </c>
       <c r="E8">
-        <v>197870</v>
+        <v>193353</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$50</c:f>
+              <c:f>Data!$A$2:$A$51</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$50</c:f>
+              <c:f>Data!$C$2:$C$51</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$8</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$9</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$8</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$9</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$8</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$9</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$8</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$9</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$8</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$9</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$8</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$9</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$8</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$9</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$8</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$9</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1838,8 +1838,38 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-15 09:00:36</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>187593</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F50"/>
+  <autoFilter ref="A1:F51"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2019,8 +2049,27 @@
         <v>193353</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>187593</v>
+      </c>
+      <c r="C9">
+        <v>187593</v>
+      </c>
+      <c r="D9">
+        <v>187593</v>
+      </c>
+      <c r="E9">
+        <v>187593</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$51</c:f>
+              <c:f>Data!$A$2:$A$52</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$51</c:f>
+              <c:f>Data!$C$2:$C$52</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1868,8 +1868,38 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:00:36</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>192273</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F51"/>
+  <autoFilter ref="A1:F52"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2059,13 +2089,13 @@
         <v>187593</v>
       </c>
       <c r="C9">
-        <v>187593</v>
+        <v>192273</v>
       </c>
       <c r="D9">
         <v>187593</v>
       </c>
       <c r="E9">
-        <v>187593</v>
+        <v>192273</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$52</c:f>
+              <c:f>Data!$A$2:$A$53</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$52</c:f>
+              <c:f>Data!$C$2:$C$53</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1898,8 +1898,38 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-17 09:00:36</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>196549</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F52"/>
+  <autoFilter ref="A1:F53"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2089,13 +2119,13 @@
         <v>187593</v>
       </c>
       <c r="C9">
-        <v>192273</v>
+        <v>196549</v>
       </c>
       <c r="D9">
         <v>187593</v>
       </c>
       <c r="E9">
-        <v>192273</v>
+        <v>196549</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$53</c:f>
+              <c:f>Data!$A$2:$A$54</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$53</c:f>
+              <c:f>Data!$C$2:$C$54</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1928,8 +1928,38 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-18 09:00:36</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>198985</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F53"/>
+  <autoFilter ref="A1:F54"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2119,13 +2149,13 @@
         <v>187593</v>
       </c>
       <c r="C9">
-        <v>196549</v>
+        <v>198985</v>
       </c>
       <c r="D9">
         <v>187593</v>
       </c>
       <c r="E9">
-        <v>196549</v>
+        <v>198985</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$54</c:f>
+              <c:f>Data!$A$2:$A$55</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$54</c:f>
+              <c:f>Data!$C$2:$C$55</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1958,8 +1958,38 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:00:36</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>200919</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F54"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2149,13 +2179,13 @@
         <v>187593</v>
       </c>
       <c r="C9">
-        <v>198985</v>
+        <v>200919</v>
       </c>
       <c r="D9">
         <v>187593</v>
       </c>
       <c r="E9">
-        <v>198985</v>
+        <v>200919</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$55</c:f>
+              <c:f>Data!$A$2:$A$56</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$55</c:f>
+              <c:f>Data!$C$2:$C$56</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -1988,8 +1988,38 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-20 09:00:36</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>199963</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F55"/>
+  <autoFilter ref="A1:F56"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2185,7 +2215,7 @@
         <v>187593</v>
       </c>
       <c r="E9">
-        <v>200919</v>
+        <v>199963</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$56</c:f>
+              <c:f>Data!$A$2:$A$57</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$56</c:f>
+              <c:f>Data!$C$2:$C$57</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2018,8 +2018,38 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:00:36</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>194959</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F56"/>
+  <autoFilter ref="A1:F57"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2215,7 +2245,7 @@
         <v>187593</v>
       </c>
       <c r="E9">
-        <v>199963</v>
+        <v>194959</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$57</c:f>
+              <c:f>Data!$A$2:$A$58</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$57</c:f>
+              <c:f>Data!$C$2:$C$58</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$9</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$10</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$9</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$10</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$9</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$10</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$9</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$10</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$9</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$10</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$9</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$10</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$9</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$10</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$9</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$10</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2048,8 +2048,38 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:00:36</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>189705</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F57"/>
+  <autoFilter ref="A1:F58"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2248,8 +2278,27 @@
         <v>194959</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>189705</v>
+      </c>
+      <c r="C10">
+        <v>189705</v>
+      </c>
+      <c r="D10">
+        <v>189705</v>
+      </c>
+      <c r="E10">
+        <v>189705</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$58</c:f>
+              <c:f>Data!$A$2:$A$59</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$58</c:f>
+              <c:f>Data!$C$2:$C$59</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2078,8 +2078,38 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:00:36</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>194401</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F58"/>
+  <autoFilter ref="A1:F59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2288,13 +2318,13 @@
         <v>189705</v>
       </c>
       <c r="C10">
-        <v>189705</v>
+        <v>194401</v>
       </c>
       <c r="D10">
         <v>189705</v>
       </c>
       <c r="E10">
-        <v>189705</v>
+        <v>194401</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$59</c:f>
+              <c:f>Data!$A$2:$A$60</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$59</c:f>
+              <c:f>Data!$C$2:$C$60</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2108,8 +2108,38 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:00:36</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>198191</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F59"/>
+  <autoFilter ref="A1:F60"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2318,13 +2348,13 @@
         <v>189705</v>
       </c>
       <c r="C10">
-        <v>194401</v>
+        <v>198191</v>
       </c>
       <c r="D10">
         <v>189705</v>
       </c>
       <c r="E10">
-        <v>194401</v>
+        <v>198191</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$60</c:f>
+              <c:f>Data!$A$2:$A$61</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$60</c:f>
+              <c:f>Data!$C$2:$C$61</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2138,8 +2138,38 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:00:36</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>202002</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F60"/>
+  <autoFilter ref="A1:F61"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2348,13 +2378,13 @@
         <v>189705</v>
       </c>
       <c r="C10">
-        <v>198191</v>
+        <v>202002</v>
       </c>
       <c r="D10">
         <v>189705</v>
       </c>
       <c r="E10">
-        <v>198191</v>
+        <v>202002</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$61</c:f>
+              <c:f>Data!$A$2:$A$62</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$61</c:f>
+              <c:f>Data!$C$2:$C$62</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2168,8 +2168,38 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-26 09:00:36</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>202975</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F61"/>
+  <autoFilter ref="A1:F62"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2378,13 +2408,13 @@
         <v>189705</v>
       </c>
       <c r="C10">
-        <v>202002</v>
+        <v>202975</v>
       </c>
       <c r="D10">
         <v>189705</v>
       </c>
       <c r="E10">
-        <v>202002</v>
+        <v>202975</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$62</c:f>
+              <c:f>Data!$A$2:$A$63</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$62</c:f>
+              <c:f>Data!$C$2:$C$63</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2198,8 +2198,38 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-27 09:00:36</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>202568</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F62"/>
+  <autoFilter ref="A1:F63"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2414,7 +2444,7 @@
         <v>189705</v>
       </c>
       <c r="E10">
-        <v>202975</v>
+        <v>202568</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$63</c:f>
+              <c:f>Data!$A$2:$A$64</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$63</c:f>
+              <c:f>Data!$C$2:$C$64</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2228,8 +2228,38 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-28 09:00:36</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>198132</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F63"/>
+  <autoFilter ref="A1:F64"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2444,7 +2474,7 @@
         <v>189705</v>
       </c>
       <c r="E10">
-        <v>202568</v>
+        <v>198132</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$64</c:f>
+              <c:f>Data!$A$2:$A$65</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$64</c:f>
+              <c:f>Data!$C$2:$C$65</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$10</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$11</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$10</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$11</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$10</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$11</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$10</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$11</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$10</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$11</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$10</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$11</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$10</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$11</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$10</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$11</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2258,8 +2258,38 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-29 09:00:36</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>193196</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F64"/>
+  <autoFilter ref="A1:F65"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2477,8 +2507,27 @@
         <v>198132</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>193196</v>
+      </c>
+      <c r="C11">
+        <v>193196</v>
+      </c>
+      <c r="D11">
+        <v>193196</v>
+      </c>
+      <c r="E11">
+        <v>193196</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$65</c:f>
+              <c:f>Data!$A$2:$A$66</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$65</c:f>
+              <c:f>Data!$C$2:$C$66</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2288,8 +2288,38 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-30 09:00:36</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>197751</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F65"/>
+  <autoFilter ref="A1:F66"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2517,13 +2547,13 @@
         <v>193196</v>
       </c>
       <c r="C11">
-        <v>193196</v>
+        <v>197751</v>
       </c>
       <c r="D11">
         <v>193196</v>
       </c>
       <c r="E11">
-        <v>193196</v>
+        <v>197751</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$66</c:f>
+              <c:f>Data!$A$2:$A$67</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$66</c:f>
+              <c:f>Data!$C$2:$C$67</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2318,8 +2318,38 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:00:36</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>192942</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F66"/>
+  <autoFilter ref="A1:F67"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2550,10 +2580,10 @@
         <v>197751</v>
       </c>
       <c r="D11">
-        <v>193196</v>
+        <v>192942</v>
       </c>
       <c r="E11">
-        <v>197751</v>
+        <v>192942</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$67</c:f>
+              <c:f>Data!$A$2:$A$68</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$67</c:f>
+              <c:f>Data!$C$2:$C$68</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2348,8 +2348,38 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:00:36</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>196771</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F67"/>
+  <autoFilter ref="A1:F68"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2583,7 +2613,7 @@
         <v>192942</v>
       </c>
       <c r="E11">
-        <v>192942</v>
+        <v>196771</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$68</c:f>
+              <c:f>Data!$A$2:$A$69</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$68</c:f>
+              <c:f>Data!$C$2:$C$69</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2378,8 +2378,38 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-03 09:00:36</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>200302</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F68"/>
+  <autoFilter ref="A1:F69"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2607,13 +2637,13 @@
         <v>193196</v>
       </c>
       <c r="C11">
-        <v>197751</v>
+        <v>200302</v>
       </c>
       <c r="D11">
         <v>192942</v>
       </c>
       <c r="E11">
-        <v>196771</v>
+        <v>200302</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$69</c:f>
+              <c:f>Data!$A$2:$A$70</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$69</c:f>
+              <c:f>Data!$C$2:$C$70</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2408,8 +2408,38 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:00:36</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>202371</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F69"/>
+  <autoFilter ref="A1:F70"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2637,13 +2667,13 @@
         <v>193196</v>
       </c>
       <c r="C11">
-        <v>200302</v>
+        <v>202371</v>
       </c>
       <c r="D11">
         <v>192942</v>
       </c>
       <c r="E11">
-        <v>200302</v>
+        <v>202371</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$70</c:f>
+              <c:f>Data!$A$2:$A$71</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$70</c:f>
+              <c:f>Data!$C$2:$C$71</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2438,8 +2438,38 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:00:36</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>199604</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F70"/>
+  <autoFilter ref="A1:F71"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2673,7 +2703,7 @@
         <v>192942</v>
       </c>
       <c r="E11">
-        <v>202371</v>
+        <v>199604</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$71</c:f>
+              <c:f>Data!$A$2:$A$72</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$71</c:f>
+              <c:f>Data!$C$2:$C$72</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$11</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$12</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$11</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$12</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$11</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$12</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$11</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$12</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$11</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$12</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$11</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$12</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$11</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$12</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$11</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$12</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2468,8 +2468,38 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-06 09:00:36</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>194164</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F71"/>
+  <autoFilter ref="A1:F72"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2706,8 +2736,27 @@
         <v>199604</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>194164</v>
+      </c>
+      <c r="C12">
+        <v>194164</v>
+      </c>
+      <c r="D12">
+        <v>194164</v>
+      </c>
+      <c r="E12">
+        <v>194164</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$72</c:f>
+              <c:f>Data!$A$2:$A$73</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$72</c:f>
+              <c:f>Data!$C$2:$C$73</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2498,8 +2498,38 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-07 09:00:36</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>198549</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F72"/>
+  <autoFilter ref="A1:F73"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2746,13 +2776,13 @@
         <v>194164</v>
       </c>
       <c r="C12">
-        <v>194164</v>
+        <v>198549</v>
       </c>
       <c r="D12">
         <v>194164</v>
       </c>
       <c r="E12">
-        <v>194164</v>
+        <v>198549</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$73</c:f>
+              <c:f>Data!$A$2:$A$74</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$73</c:f>
+              <c:f>Data!$C$2:$C$74</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2528,8 +2528,38 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:00:36</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>202100</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F73"/>
+  <autoFilter ref="A1:F74"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2776,13 +2806,13 @@
         <v>194164</v>
       </c>
       <c r="C12">
-        <v>198549</v>
+        <v>202100</v>
       </c>
       <c r="D12">
         <v>194164</v>
       </c>
       <c r="E12">
-        <v>198549</v>
+        <v>202100</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$74</c:f>
+              <c:f>Data!$A$2:$A$75</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$74</c:f>
+              <c:f>Data!$C$2:$C$75</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2558,8 +2558,38 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-09 09:00:36</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>204263</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F74"/>
+  <autoFilter ref="A1:F75"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2806,13 +2836,13 @@
         <v>194164</v>
       </c>
       <c r="C12">
-        <v>202100</v>
+        <v>204263</v>
       </c>
       <c r="D12">
         <v>194164</v>
       </c>
       <c r="E12">
-        <v>202100</v>
+        <v>204263</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$75</c:f>
+              <c:f>Data!$A$2:$A$76</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$75</c:f>
+              <c:f>Data!$C$2:$C$76</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2588,8 +2588,38 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-10 09:00:36</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>206346</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F75"/>
+  <autoFilter ref="A1:F76"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2836,13 +2866,13 @@
         <v>194164</v>
       </c>
       <c r="C12">
-        <v>204263</v>
+        <v>206346</v>
       </c>
       <c r="D12">
         <v>194164</v>
       </c>
       <c r="E12">
-        <v>204263</v>
+        <v>206346</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$76</c:f>
+              <c:f>Data!$A$2:$A$77</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$76</c:f>
+              <c:f>Data!$C$2:$C$77</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2618,8 +2618,38 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-11 09:00:36</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>204943</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F76"/>
+  <autoFilter ref="A1:F77"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2872,7 +2902,7 @@
         <v>194164</v>
       </c>
       <c r="E12">
-        <v>206346</v>
+        <v>204943</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$77</c:f>
+              <c:f>Data!$A$2:$A$78</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$77</c:f>
+              <c:f>Data!$C$2:$C$78</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2648,8 +2648,38 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:00:36</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>200348</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F77"/>
+  <autoFilter ref="A1:F78"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2902,7 +2932,7 @@
         <v>194164</v>
       </c>
       <c r="E12">
-        <v>204943</v>
+        <v>200348</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$78</c:f>
+              <c:f>Data!$A$2:$A$79</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$78</c:f>
+              <c:f>Data!$C$2:$C$79</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$12</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$13</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$12</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$13</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$12</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$13</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$12</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$13</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$12</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$13</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$12</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$13</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$12</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$13</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$12</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$13</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2678,8 +2678,38 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-13 09:00:36</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>195004</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F78"/>
+  <autoFilter ref="A1:F79"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2935,8 +2965,27 @@
         <v>200348</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>195004</v>
+      </c>
+      <c r="C13">
+        <v>195004</v>
+      </c>
+      <c r="D13">
+        <v>195004</v>
+      </c>
+      <c r="E13">
+        <v>195004</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$79</c:f>
+              <c:f>Data!$A$2:$A$80</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$79</c:f>
+              <c:f>Data!$C$2:$C$80</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2708,8 +2708,38 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:00:36</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>199299</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F79"/>
+  <autoFilter ref="A1:F80"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2975,13 +3005,13 @@
         <v>195004</v>
       </c>
       <c r="C13">
-        <v>195004</v>
+        <v>199299</v>
       </c>
       <c r="D13">
         <v>195004</v>
       </c>
       <c r="E13">
-        <v>195004</v>
+        <v>199299</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$80</c:f>
+              <c:f>Data!$A$2:$A$81</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$80</c:f>
+              <c:f>Data!$C$2:$C$81</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2738,8 +2738,38 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:00:36</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>202443</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F80"/>
+  <autoFilter ref="A1:F81"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3005,13 +3035,13 @@
         <v>195004</v>
       </c>
       <c r="C13">
-        <v>199299</v>
+        <v>202443</v>
       </c>
       <c r="D13">
         <v>195004</v>
       </c>
       <c r="E13">
-        <v>199299</v>
+        <v>202443</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$81</c:f>
+              <c:f>Data!$A$2:$A$82</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$81</c:f>
+              <c:f>Data!$C$2:$C$82</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2768,8 +2768,38 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:00:36</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>202533</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F81"/>
+  <autoFilter ref="A1:F82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3035,13 +3065,13 @@
         <v>195004</v>
       </c>
       <c r="C13">
-        <v>202443</v>
+        <v>202533</v>
       </c>
       <c r="D13">
         <v>195004</v>
       </c>
       <c r="E13">
-        <v>202443</v>
+        <v>202533</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$82</c:f>
+              <c:f>Data!$A$2:$A$83</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$82</c:f>
+              <c:f>Data!$C$2:$C$83</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2798,8 +2798,38 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-17 09:00:36</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>204865</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F82"/>
+  <autoFilter ref="A1:F83"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3065,13 +3095,13 @@
         <v>195004</v>
       </c>
       <c r="C13">
-        <v>202533</v>
+        <v>204865</v>
       </c>
       <c r="D13">
         <v>195004</v>
       </c>
       <c r="E13">
-        <v>202533</v>
+        <v>204865</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$83</c:f>
+              <c:f>Data!$A$2:$A$84</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$83</c:f>
+              <c:f>Data!$C$2:$C$84</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2828,8 +2828,38 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-18 09:00:36</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>198957</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F83"/>
+  <autoFilter ref="A1:F84"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3101,7 +3131,7 @@
         <v>195004</v>
       </c>
       <c r="E13">
-        <v>204865</v>
+        <v>198957</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$84</c:f>
+              <c:f>Data!$A$2:$A$85</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$84</c:f>
+              <c:f>Data!$C$2:$C$85</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2858,8 +2858,38 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:00:36</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>194007</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F84"/>
+  <autoFilter ref="A1:F85"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3128,10 +3158,10 @@
         <v>204865</v>
       </c>
       <c r="D13">
-        <v>195004</v>
+        <v>194007</v>
       </c>
       <c r="E13">
-        <v>198957</v>
+        <v>194007</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$85</c:f>
+              <c:f>Data!$A$2:$A$86</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$85</c:f>
+              <c:f>Data!$C$2:$C$86</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$13</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$14</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$13</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$14</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$13</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$14</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$13</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$14</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$13</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$14</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$13</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$14</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$13</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$14</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$13</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$14</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2888,8 +2888,38 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:00:36</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>189067</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F85"/>
+  <autoFilter ref="A1:F86"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3164,8 +3194,27 @@
         <v>194007</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>189067</v>
+      </c>
+      <c r="C14">
+        <v>189067</v>
+      </c>
+      <c r="D14">
+        <v>189067</v>
+      </c>
+      <c r="E14">
+        <v>189067</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$86</c:f>
+              <c:f>Data!$A$2:$A$87</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$86</c:f>
+              <c:f>Data!$C$2:$C$87</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2918,8 +2918,38 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-21 09:00:36</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>193672</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F86"/>
+  <autoFilter ref="A1:F87"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3204,13 +3234,13 @@
         <v>189067</v>
       </c>
       <c r="C14">
-        <v>189067</v>
+        <v>193672</v>
       </c>
       <c r="D14">
         <v>189067</v>
       </c>
       <c r="E14">
-        <v>189067</v>
+        <v>193672</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$87</c:f>
+              <c:f>Data!$A$2:$A$88</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$87</c:f>
+              <c:f>Data!$C$2:$C$88</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2948,8 +2948,38 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-22 09:00:36</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>197708</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F87"/>
+  <autoFilter ref="A1:F88"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3234,13 +3264,13 @@
         <v>189067</v>
       </c>
       <c r="C14">
-        <v>193672</v>
+        <v>197708</v>
       </c>
       <c r="D14">
         <v>189067</v>
       </c>
       <c r="E14">
-        <v>193672</v>
+        <v>197708</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$88</c:f>
+              <c:f>Data!$A$2:$A$89</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$88</c:f>
+              <c:f>Data!$C$2:$C$89</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -2978,8 +2978,38 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-23 09:00:36</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>199505</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F88"/>
+  <autoFilter ref="A1:F89"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3264,13 +3294,13 @@
         <v>189067</v>
       </c>
       <c r="C14">
-        <v>197708</v>
+        <v>199505</v>
       </c>
       <c r="D14">
         <v>189067</v>
       </c>
       <c r="E14">
-        <v>197708</v>
+        <v>199505</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$89</c:f>
+              <c:f>Data!$A$2:$A$90</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$89</c:f>
+              <c:f>Data!$C$2:$C$90</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3008,8 +3008,38 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:00:36</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>201540</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F89"/>
+  <autoFilter ref="A1:F90"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3294,13 +3324,13 @@
         <v>189067</v>
       </c>
       <c r="C14">
-        <v>199505</v>
+        <v>201540</v>
       </c>
       <c r="D14">
         <v>189067</v>
       </c>
       <c r="E14">
-        <v>199505</v>
+        <v>201540</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$90</c:f>
+              <c:f>Data!$A$2:$A$91</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$90</c:f>
+              <c:f>Data!$C$2:$C$91</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3038,8 +3038,38 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-25 09:00:36</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>202812</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F90"/>
+  <autoFilter ref="A1:F91"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3324,13 +3354,13 @@
         <v>189067</v>
       </c>
       <c r="C14">
-        <v>201540</v>
+        <v>202812</v>
       </c>
       <c r="D14">
         <v>189067</v>
       </c>
       <c r="E14">
-        <v>201540</v>
+        <v>202812</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$91</c:f>
+              <c:f>Data!$A$2:$A$92</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$91</c:f>
+              <c:f>Data!$C$2:$C$92</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3068,8 +3068,38 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-26 09:00:36</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>197749</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F91"/>
+  <autoFilter ref="A1:F92"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3360,7 +3390,7 @@
         <v>189067</v>
       </c>
       <c r="E14">
-        <v>202812</v>
+        <v>197749</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$92</c:f>
+              <c:f>Data!$A$2:$A$93</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$92</c:f>
+              <c:f>Data!$C$2:$C$93</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$14</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$15</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$14</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$15</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$14</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$15</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$14</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$15</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$14</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$15</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$14</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$15</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$14</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$15</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$14</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$15</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3098,8 +3098,38 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-27 09:00:36</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>192790</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F92"/>
+  <autoFilter ref="A1:F93"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3393,8 +3423,27 @@
         <v>197749</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>192790</v>
+      </c>
+      <c r="C15">
+        <v>192790</v>
+      </c>
+      <c r="D15">
+        <v>192790</v>
+      </c>
+      <c r="E15">
+        <v>192790</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$93</c:f>
+              <c:f>Data!$A$2:$A$94</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$93</c:f>
+              <c:f>Data!$C$2:$C$94</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3128,8 +3128,38 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:00:36</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>196873</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F93"/>
+  <autoFilter ref="A1:F94"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3433,13 +3463,13 @@
         <v>192790</v>
       </c>
       <c r="C15">
-        <v>192790</v>
+        <v>196873</v>
       </c>
       <c r="D15">
         <v>192790</v>
       </c>
       <c r="E15">
-        <v>192790</v>
+        <v>196873</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$94</c:f>
+              <c:f>Data!$A$2:$A$95</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$94</c:f>
+              <c:f>Data!$C$2:$C$95</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3158,8 +3158,38 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:00:36</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>199587</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F94"/>
+  <autoFilter ref="A1:F95"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3463,13 +3493,13 @@
         <v>192790</v>
       </c>
       <c r="C15">
-        <v>196873</v>
+        <v>199587</v>
       </c>
       <c r="D15">
         <v>192790</v>
       </c>
       <c r="E15">
-        <v>196873</v>
+        <v>199587</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$95</c:f>
+              <c:f>Data!$A$2:$A$96</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$95</c:f>
+              <c:f>Data!$C$2:$C$96</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3188,8 +3188,38 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-30 09:00:36</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>201058</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F95"/>
+  <autoFilter ref="A1:F96"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3493,13 +3523,13 @@
         <v>192790</v>
       </c>
       <c r="C15">
-        <v>199587</v>
+        <v>201058</v>
       </c>
       <c r="D15">
         <v>192790</v>
       </c>
       <c r="E15">
-        <v>199587</v>
+        <v>201058</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$96</c:f>
+              <c:f>Data!$A$2:$A$97</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$96</c:f>
+              <c:f>Data!$C$2:$C$97</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3218,8 +3218,38 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-31 09:00:36</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>201810</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F96"/>
+  <autoFilter ref="A1:F97"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3523,13 +3553,13 @@
         <v>192790</v>
       </c>
       <c r="C15">
-        <v>201058</v>
+        <v>201810</v>
       </c>
       <c r="D15">
         <v>192790</v>
       </c>
       <c r="E15">
-        <v>201058</v>
+        <v>201810</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$97</c:f>
+              <c:f>Data!$A$2:$A$98</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$97</c:f>
+              <c:f>Data!$C$2:$C$98</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3248,8 +3248,38 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:00:36</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>193122</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F97"/>
+  <autoFilter ref="A1:F98"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3559,7 +3589,7 @@
         <v>192790</v>
       </c>
       <c r="E15">
-        <v>201810</v>
+        <v>193122</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$98</c:f>
+              <c:f>Data!$A$2:$A$99</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$98</c:f>
+              <c:f>Data!$C$2:$C$99</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3278,8 +3278,38 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-02 09:00:36</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>188911</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F98"/>
+  <autoFilter ref="A1:F99"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3586,10 +3616,10 @@
         <v>201810</v>
       </c>
       <c r="D15">
-        <v>192790</v>
+        <v>188911</v>
       </c>
       <c r="E15">
-        <v>193122</v>
+        <v>188911</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$99</c:f>
+              <c:f>Data!$A$2:$A$100</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$99</c:f>
+              <c:f>Data!$C$2:$C$100</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$15</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$16</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$15</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$16</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$15</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$16</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$15</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$16</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$15</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$16</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$15</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$16</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$15</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$16</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$15</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$16</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3308,8 +3308,38 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-03 09:00:36</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>185457</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F99"/>
+  <autoFilter ref="A1:F100"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3622,8 +3652,27 @@
         <v>188911</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>185457</v>
+      </c>
+      <c r="C16">
+        <v>185457</v>
+      </c>
+      <c r="D16">
+        <v>185457</v>
+      </c>
+      <c r="E16">
+        <v>185457</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$100</c:f>
+              <c:f>Data!$A$2:$A$101</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$100</c:f>
+              <c:f>Data!$C$2:$C$101</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3338,8 +3338,38 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-04 09:00:36</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>189826</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F100"/>
+  <autoFilter ref="A1:F101"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3662,13 +3692,13 @@
         <v>185457</v>
       </c>
       <c r="C16">
-        <v>185457</v>
+        <v>189826</v>
       </c>
       <c r="D16">
         <v>185457</v>
       </c>
       <c r="E16">
-        <v>185457</v>
+        <v>189826</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$101</c:f>
+              <c:f>Data!$A$2:$A$102</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$101</c:f>
+              <c:f>Data!$C$2:$C$102</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3368,8 +3368,38 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:00:36</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>193305</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F101"/>
+  <autoFilter ref="A1:F102"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3692,13 +3722,13 @@
         <v>185457</v>
       </c>
       <c r="C16">
-        <v>189826</v>
+        <v>193305</v>
       </c>
       <c r="D16">
         <v>185457</v>
       </c>
       <c r="E16">
-        <v>189826</v>
+        <v>193305</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$102</c:f>
+              <c:f>Data!$A$2:$A$103</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$102</c:f>
+              <c:f>Data!$C$2:$C$103</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3398,8 +3398,38 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-06 09:00:36</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>195262</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F102"/>
+  <autoFilter ref="A1:F103"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3722,13 +3752,13 @@
         <v>185457</v>
       </c>
       <c r="C16">
-        <v>193305</v>
+        <v>195262</v>
       </c>
       <c r="D16">
         <v>185457</v>
       </c>
       <c r="E16">
-        <v>193305</v>
+        <v>195262</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$103</c:f>
+              <c:f>Data!$A$2:$A$104</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$103</c:f>
+              <c:f>Data!$C$2:$C$104</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3428,8 +3428,38 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:00:36</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>197755</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F103"/>
+  <autoFilter ref="A1:F104"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3752,13 +3782,13 @@
         <v>185457</v>
       </c>
       <c r="C16">
-        <v>195262</v>
+        <v>197755</v>
       </c>
       <c r="D16">
         <v>185457</v>
       </c>
       <c r="E16">
-        <v>195262</v>
+        <v>197755</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$104</c:f>
+              <c:f>Data!$A$2:$A$105</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$104</c:f>
+              <c:f>Data!$C$2:$C$105</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3458,8 +3458,38 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-08 09:00:36</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>197391</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F104"/>
+  <autoFilter ref="A1:F105"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3788,7 +3818,7 @@
         <v>185457</v>
       </c>
       <c r="E16">
-        <v>197755</v>
+        <v>197391</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$105</c:f>
+              <c:f>Data!$A$2:$A$106</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$105</c:f>
+              <c:f>Data!$C$2:$C$106</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3488,8 +3488,38 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:00:36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>192671</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F105"/>
+  <autoFilter ref="A1:F106"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3818,7 +3848,7 @@
         <v>185457</v>
       </c>
       <c r="E16">
-        <v>197391</v>
+        <v>192671</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$106</c:f>
+              <c:f>Data!$A$2:$A$107</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$106</c:f>
+              <c:f>Data!$C$2:$C$107</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$16</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$17</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$16</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$17</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$16</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$17</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$16</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$17</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$16</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$17</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$16</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$17</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$16</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$17</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$16</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$17</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3518,8 +3518,38 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:00:36</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>187606</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F106"/>
+  <autoFilter ref="A1:F107"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3851,8 +3881,27 @@
         <v>192671</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>187606</v>
+      </c>
+      <c r="C17">
+        <v>187606</v>
+      </c>
+      <c r="D17">
+        <v>187606</v>
+      </c>
+      <c r="E17">
+        <v>187606</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$107</c:f>
+              <c:f>Data!$A$2:$A$108</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$107</c:f>
+              <c:f>Data!$C$2:$C$108</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3548,8 +3548,38 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:00:36</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>191850</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F107"/>
+  <autoFilter ref="A1:F108"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3891,13 +3921,13 @@
         <v>187606</v>
       </c>
       <c r="C17">
-        <v>187606</v>
+        <v>191850</v>
       </c>
       <c r="D17">
         <v>187606</v>
       </c>
       <c r="E17">
-        <v>187606</v>
+        <v>191850</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$108</c:f>
+              <c:f>Data!$A$2:$A$109</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$108</c:f>
+              <c:f>Data!$C$2:$C$109</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3578,8 +3578,38 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:00:36</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>196271</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F108"/>
+  <autoFilter ref="A1:F109"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3921,13 +3951,13 @@
         <v>187606</v>
       </c>
       <c r="C17">
-        <v>191850</v>
+        <v>196271</v>
       </c>
       <c r="D17">
         <v>187606</v>
       </c>
       <c r="E17">
-        <v>191850</v>
+        <v>196271</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$109</c:f>
+              <c:f>Data!$A$2:$A$110</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$109</c:f>
+              <c:f>Data!$C$2:$C$110</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3608,8 +3608,38 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-13 09:00:36</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>198228</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F109"/>
+  <autoFilter ref="A1:F110"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3951,13 +3981,13 @@
         <v>187606</v>
       </c>
       <c r="C17">
-        <v>196271</v>
+        <v>198228</v>
       </c>
       <c r="D17">
         <v>187606</v>
       </c>
       <c r="E17">
-        <v>196271</v>
+        <v>198228</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$110</c:f>
+              <c:f>Data!$A$2:$A$111</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$110</c:f>
+              <c:f>Data!$C$2:$C$111</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3638,8 +3638,38 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:00:36</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>200754</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F110"/>
+  <autoFilter ref="A1:F111"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3981,13 +4011,13 @@
         <v>187606</v>
       </c>
       <c r="C17">
-        <v>198228</v>
+        <v>200754</v>
       </c>
       <c r="D17">
         <v>187606</v>
       </c>
       <c r="E17">
-        <v>198228</v>
+        <v>200754</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$111</c:f>
+              <c:f>Data!$A$2:$A$112</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$111</c:f>
+              <c:f>Data!$C$2:$C$112</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3668,8 +3668,38 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:00:36</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>199771</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F111"/>
+  <autoFilter ref="A1:F112"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4017,7 +4047,7 @@
         <v>187606</v>
       </c>
       <c r="E17">
-        <v>200754</v>
+        <v>199771</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$112</c:f>
+              <c:f>Data!$A$2:$A$113</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$112</c:f>
+              <c:f>Data!$C$2:$C$113</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3698,8 +3698,38 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-16 09:00:36</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>194735</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F112"/>
+  <autoFilter ref="A1:F113"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4047,7 +4077,7 @@
         <v>187606</v>
       </c>
       <c r="E17">
-        <v>199771</v>
+        <v>194735</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$113</c:f>
+              <c:f>Data!$A$2:$A$114</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$113</c:f>
+              <c:f>Data!$C$2:$C$114</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$17</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$18</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$17</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$18</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$17</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$18</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$17</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$18</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$17</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$18</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$17</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$18</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$17</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$18</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$17</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$18</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3728,8 +3728,38 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:00:36</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>191381</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F113"/>
+  <autoFilter ref="A1:F114"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4080,8 +4110,27 @@
         <v>194735</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>191381</v>
+      </c>
+      <c r="C18">
+        <v>191381</v>
+      </c>
+      <c r="D18">
+        <v>191381</v>
+      </c>
+      <c r="E18">
+        <v>191381</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$114</c:f>
+              <c:f>Data!$A$2:$A$115</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$114</c:f>
+              <c:f>Data!$C$2:$C$115</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3758,8 +3758,38 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:00:36</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>187876</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F114"/>
+  <autoFilter ref="A1:F115"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4123,10 +4153,10 @@
         <v>191381</v>
       </c>
       <c r="D18">
-        <v>191381</v>
+        <v>187876</v>
       </c>
       <c r="E18">
-        <v>191381</v>
+        <v>187876</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$115</c:f>
+              <c:f>Data!$A$2:$A$116</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$115</c:f>
+              <c:f>Data!$C$2:$C$116</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3788,8 +3788,38 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:00:36</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>193755</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F115"/>
+  <autoFilter ref="A1:F116"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4150,13 +4180,13 @@
         <v>191381</v>
       </c>
       <c r="C18">
-        <v>191381</v>
+        <v>193755</v>
       </c>
       <c r="D18">
         <v>187876</v>
       </c>
       <c r="E18">
-        <v>187876</v>
+        <v>193755</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$116</c:f>
+              <c:f>Data!$A$2:$A$117</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$116</c:f>
+              <c:f>Data!$C$2:$C$117</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3818,8 +3818,38 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:00:36</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>197098</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F116"/>
+  <autoFilter ref="A1:F117"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4180,13 +4210,13 @@
         <v>191381</v>
       </c>
       <c r="C18">
-        <v>193755</v>
+        <v>197098</v>
       </c>
       <c r="D18">
         <v>187876</v>
       </c>
       <c r="E18">
-        <v>193755</v>
+        <v>197098</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$117</c:f>
+              <c:f>Data!$A$2:$A$118</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$117</c:f>
+              <c:f>Data!$C$2:$C$118</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3848,8 +3848,38 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:36</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>199244</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F117"/>
+  <autoFilter ref="A1:F118"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4210,13 +4240,13 @@
         <v>191381</v>
       </c>
       <c r="C18">
-        <v>197098</v>
+        <v>199244</v>
       </c>
       <c r="D18">
         <v>187876</v>
       </c>
       <c r="E18">
-        <v>197098</v>
+        <v>199244</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$118</c:f>
+              <c:f>Data!$A$2:$A$119</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$118</c:f>
+              <c:f>Data!$C$2:$C$119</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3878,8 +3878,38 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-22 09:00:36</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>199226</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F118"/>
+  <autoFilter ref="A1:F119"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4246,7 +4276,7 @@
         <v>187876</v>
       </c>
       <c r="E18">
-        <v>199244</v>
+        <v>199226</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$119</c:f>
+              <c:f>Data!$A$2:$A$120</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$119</c:f>
+              <c:f>Data!$C$2:$C$120</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3908,8 +3908,38 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-23 09:00:36</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>194753</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F119"/>
+  <autoFilter ref="A1:F120"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4276,7 +4306,7 @@
         <v>187876</v>
       </c>
       <c r="E18">
-        <v>199226</v>
+        <v>194753</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$120</c:f>
+              <c:f>Data!$A$2:$A$121</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$120</c:f>
+              <c:f>Data!$C$2:$C$121</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$18</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$19</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$18</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$19</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$18</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$19</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$18</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$19</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$18</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$19</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$18</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$19</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$18</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$19</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$18</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$19</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3938,8 +3938,38 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:00:36</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>189719</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F120"/>
+  <autoFilter ref="A1:F121"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4309,8 +4339,27 @@
         <v>194753</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>189719</v>
+      </c>
+      <c r="C19">
+        <v>189719</v>
+      </c>
+      <c r="D19">
+        <v>189719</v>
+      </c>
+      <c r="E19">
+        <v>189719</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E18"/>
+  <autoFilter ref="A1:E19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$121</c:f>
+              <c:f>Data!$A$2:$A$122</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$121</c:f>
+              <c:f>Data!$C$2:$C$122</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3968,8 +3968,38 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:00:36</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>194578</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F121"/>
+  <autoFilter ref="A1:F122"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4349,13 +4379,13 @@
         <v>189719</v>
       </c>
       <c r="C19">
-        <v>189719</v>
+        <v>194578</v>
       </c>
       <c r="D19">
         <v>189719</v>
       </c>
       <c r="E19">
-        <v>189719</v>
+        <v>194578</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$122</c:f>
+              <c:f>Data!$A$2:$A$123</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$122</c:f>
+              <c:f>Data!$C$2:$C$123</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -3998,8 +3998,38 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:00:36</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>198322</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F122"/>
+  <autoFilter ref="A1:F123"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4379,13 +4409,13 @@
         <v>189719</v>
       </c>
       <c r="C19">
-        <v>194578</v>
+        <v>198322</v>
       </c>
       <c r="D19">
         <v>189719</v>
       </c>
       <c r="E19">
-        <v>194578</v>
+        <v>198322</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$123</c:f>
+              <c:f>Data!$A$2:$A$124</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$123</c:f>
+              <c:f>Data!$C$2:$C$124</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4028,8 +4028,38 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-27 09:00:36</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>200793</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F123"/>
+  <autoFilter ref="A1:F124"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4409,13 +4439,13 @@
         <v>189719</v>
       </c>
       <c r="C19">
-        <v>198322</v>
+        <v>200793</v>
       </c>
       <c r="D19">
         <v>189719</v>
       </c>
       <c r="E19">
-        <v>198322</v>
+        <v>200793</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$124</c:f>
+              <c:f>Data!$A$2:$A$125</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$124</c:f>
+              <c:f>Data!$C$2:$C$125</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4058,8 +4058,38 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:00:36</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>203170</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F124"/>
+  <autoFilter ref="A1:F125"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4439,13 +4469,13 @@
         <v>189719</v>
       </c>
       <c r="C19">
-        <v>200793</v>
+        <v>203170</v>
       </c>
       <c r="D19">
         <v>189719</v>
       </c>
       <c r="E19">
-        <v>200793</v>
+        <v>203170</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$125</c:f>
+              <c:f>Data!$A$2:$A$126</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$125</c:f>
+              <c:f>Data!$C$2:$C$126</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4088,8 +4088,38 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-29 09:00:36</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>203060</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F125"/>
+  <autoFilter ref="A1:F126"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4475,7 +4505,7 @@
         <v>189719</v>
       </c>
       <c r="E19">
-        <v>203170</v>
+        <v>203060</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$126</c:f>
+              <c:f>Data!$A$2:$A$127</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$126</c:f>
+              <c:f>Data!$C$2:$C$127</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4118,8 +4118,38 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-30 09:00:36</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>198768</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F126"/>
+  <autoFilter ref="A1:F127"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4505,7 +4535,7 @@
         <v>189719</v>
       </c>
       <c r="E19">
-        <v>203060</v>
+        <v>198768</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$127</c:f>
+              <c:f>Data!$A$2:$A$128</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$127</c:f>
+              <c:f>Data!$C$2:$C$128</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$19</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$20</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$19</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$20</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$19</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$20</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$19</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$20</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$19</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$20</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$19</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$20</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$19</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$20</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$19</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$20</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4148,8 +4148,38 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:00:36</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>194585</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F127"/>
+  <autoFilter ref="A1:F128"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4538,8 +4568,27 @@
         <v>198768</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>194585</v>
+      </c>
+      <c r="C20">
+        <v>194585</v>
+      </c>
+      <c r="D20">
+        <v>194585</v>
+      </c>
+      <c r="E20">
+        <v>194585</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$128</c:f>
+              <c:f>Data!$A$2:$A$129</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$128</c:f>
+              <c:f>Data!$C$2:$C$129</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4178,8 +4178,38 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:00:36</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>191001</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F128"/>
+  <autoFilter ref="A1:F129"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4581,10 +4611,10 @@
         <v>194585</v>
       </c>
       <c r="D20">
-        <v>194585</v>
+        <v>191001</v>
       </c>
       <c r="E20">
-        <v>194585</v>
+        <v>191001</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$129</c:f>
+              <c:f>Data!$A$2:$A$130</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$129</c:f>
+              <c:f>Data!$C$2:$C$130</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4208,8 +4208,38 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:00:36</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>195834</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F129"/>
+  <autoFilter ref="A1:F130"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4608,13 +4638,13 @@
         <v>194585</v>
       </c>
       <c r="C20">
-        <v>194585</v>
+        <v>195834</v>
       </c>
       <c r="D20">
         <v>191001</v>
       </c>
       <c r="E20">
-        <v>191001</v>
+        <v>195834</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$130</c:f>
+              <c:f>Data!$A$2:$A$131</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$130</c:f>
+              <c:f>Data!$C$2:$C$131</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4238,8 +4238,38 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:00:36</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>197857</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F130"/>
+  <autoFilter ref="A1:F131"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4638,13 +4668,13 @@
         <v>194585</v>
       </c>
       <c r="C20">
-        <v>195834</v>
+        <v>197857</v>
       </c>
       <c r="D20">
         <v>191001</v>
       </c>
       <c r="E20">
-        <v>195834</v>
+        <v>197857</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$131</c:f>
+              <c:f>Data!$A$2:$A$132</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$131</c:f>
+              <c:f>Data!$C$2:$C$132</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4268,8 +4268,38 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:00:36</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>200644</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F131"/>
+  <autoFilter ref="A1:F132"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4668,13 +4698,13 @@
         <v>194585</v>
       </c>
       <c r="C20">
-        <v>197857</v>
+        <v>200644</v>
       </c>
       <c r="D20">
         <v>191001</v>
       </c>
       <c r="E20">
-        <v>197857</v>
+        <v>200644</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$132</c:f>
+              <c:f>Data!$A$2:$A$133</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$132</c:f>
+              <c:f>Data!$C$2:$C$133</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4298,8 +4298,38 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-05 09:00:36</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>202520</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F132"/>
+  <autoFilter ref="A1:F133"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4698,13 +4728,13 @@
         <v>194585</v>
       </c>
       <c r="C20">
-        <v>200644</v>
+        <v>202520</v>
       </c>
       <c r="D20">
         <v>191001</v>
       </c>
       <c r="E20">
-        <v>200644</v>
+        <v>202520</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$133</c:f>
+              <c:f>Data!$A$2:$A$134</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$133</c:f>
+              <c:f>Data!$C$2:$C$134</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4328,8 +4328,38 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:00:36</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>197643</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F133"/>
+  <autoFilter ref="A1:F134"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4734,7 +4764,7 @@
         <v>191001</v>
       </c>
       <c r="E20">
-        <v>202520</v>
+        <v>197643</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$134</c:f>
+              <c:f>Data!$A$2:$A$135</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$134</c:f>
+              <c:f>Data!$C$2:$C$135</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$20</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$21</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$20</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$21</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$20</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$21</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$20</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$21</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$20</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$21</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$20</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$21</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$20</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$21</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$20</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$21</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4358,8 +4358,38 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:00:36</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>192228</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F134"/>
+  <autoFilter ref="A1:F135"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4767,8 +4797,27 @@
         <v>197643</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>192228</v>
+      </c>
+      <c r="C21">
+        <v>192228</v>
+      </c>
+      <c r="D21">
+        <v>192228</v>
+      </c>
+      <c r="E21">
+        <v>192228</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$135</c:f>
+              <c:f>Data!$A$2:$A$136</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$135</c:f>
+              <c:f>Data!$C$2:$C$136</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4388,8 +4388,38 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:00:36</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>197344</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F135"/>
+  <autoFilter ref="A1:F136"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4807,13 +4837,13 @@
         <v>192228</v>
       </c>
       <c r="C21">
-        <v>192228</v>
+        <v>197344</v>
       </c>
       <c r="D21">
         <v>192228</v>
       </c>
       <c r="E21">
-        <v>192228</v>
+        <v>197344</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$136</c:f>
+              <c:f>Data!$A$2:$A$137</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$136</c:f>
+              <c:f>Data!$C$2:$C$137</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4418,8 +4418,38 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:00:36</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>201195</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F136"/>
+  <autoFilter ref="A1:F137"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4837,13 +4867,13 @@
         <v>192228</v>
       </c>
       <c r="C21">
-        <v>197344</v>
+        <v>201195</v>
       </c>
       <c r="D21">
         <v>192228</v>
       </c>
       <c r="E21">
-        <v>197344</v>
+        <v>201195</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$137</c:f>
+              <c:f>Data!$A$2:$A$138</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$137</c:f>
+              <c:f>Data!$C$2:$C$138</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4448,8 +4448,38 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:00:36</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>202464</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F137"/>
+  <autoFilter ref="A1:F138"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4867,13 +4897,13 @@
         <v>192228</v>
       </c>
       <c r="C21">
-        <v>201195</v>
+        <v>202464</v>
       </c>
       <c r="D21">
         <v>192228</v>
       </c>
       <c r="E21">
-        <v>201195</v>
+        <v>202464</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$138</c:f>
+              <c:f>Data!$A$2:$A$139</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$138</c:f>
+              <c:f>Data!$C$2:$C$139</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4478,8 +4478,38 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:00:36</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>203415</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F138"/>
+  <autoFilter ref="A1:F139"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4897,13 +4927,13 @@
         <v>192228</v>
       </c>
       <c r="C21">
-        <v>202464</v>
+        <v>203415</v>
       </c>
       <c r="D21">
         <v>192228</v>
       </c>
       <c r="E21">
-        <v>202464</v>
+        <v>203415</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$139</c:f>
+              <c:f>Data!$A$2:$A$140</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$139</c:f>
+              <c:f>Data!$C$2:$C$140</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4508,8 +4508,38 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-12 09:00:36</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>203794</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F139"/>
+  <autoFilter ref="A1:F140"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4927,13 +4957,13 @@
         <v>192228</v>
       </c>
       <c r="C21">
-        <v>203415</v>
+        <v>203794</v>
       </c>
       <c r="D21">
         <v>192228</v>
       </c>
       <c r="E21">
-        <v>203415</v>
+        <v>203794</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$140</c:f>
+              <c:f>Data!$A$2:$A$141</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$140</c:f>
+              <c:f>Data!$C$2:$C$141</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4538,8 +4538,38 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:00:36</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>198797</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F140"/>
+  <autoFilter ref="A1:F141"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4963,7 +4993,7 @@
         <v>192228</v>
       </c>
       <c r="E21">
-        <v>203794</v>
+        <v>198797</v>
       </c>
     </row>
   </sheetData>
